--- a/request_forms/020_find_dentist--request_forms.xlsx
+++ b/request_forms/020_find_dentist--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'check_up'}</t>
+          <t>check_up</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Check up'}</t>
+          <t>Check up</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cleaning'}</t>
+          <t>cleaning</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cleaning'}</t>
+          <t>Cleaning</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'implant'}</t>
+          <t>implant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Implant'}</t>
+          <t>Implant</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pedodontics'}</t>
+          <t>pedodontics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pedodontics'}</t>
+          <t>Pedodontics</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'orthodontics'}</t>
+          <t>orthodontics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Orthodontics'}</t>
+          <t>Orthodontics</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'oral_surgery'}</t>
+          <t>oral_surgery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Oral Surgery'}</t>
+          <t>Oral Surgery</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_office'}</t>
+          <t>in_office</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Office'}</t>
+          <t>In Office</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_home'}</t>
+          <t>in_home</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Home'}</t>
+          <t>In Home</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'over_the_phone'}</t>
+          <t>over_the_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Over the Phone'}</t>
+          <t>Over the Phone</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'insurance'}</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Insurance'}</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
